--- a/source/8、绩效异常岗位/7、扫描岗/扫描岗-5月.xlsx
+++ b/source/8、绩效异常岗位/7、扫描岗/扫描岗-5月.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2376" uniqueCount="127">
   <si>
     <t>数据日期</t>
   </si>
@@ -404,6 +404,12 @@
   </si>
   <si>
     <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1343,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H513"/>
+  <dimension ref="A1:H549"/>
   <sheetFormatPr defaultColWidth="12.6363636363636" defaultRowHeight="20" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="16384" width="12.6363636363636" style="1" customWidth="1"/>
@@ -14679,6 +14685,942 @@
       </c>
       <c r="H513" s="1">
         <v>32</v>
+      </c>
+    </row>
+    <row r="514" customHeight="1" spans="1:8">
+      <c r="A514" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E514" s="1">
+        <v>110.5</v>
+      </c>
+      <c r="F514" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="G514" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H514" s="1">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="515" customHeight="1" spans="1:8">
+      <c r="A515" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E515" s="1">
+        <v>80.2</v>
+      </c>
+      <c r="F515" s="1">
+        <v>20.3</v>
+      </c>
+      <c r="G515" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H515" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="516" customHeight="1" spans="1:8">
+      <c r="A516" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E516" s="1">
+        <v>137.2</v>
+      </c>
+      <c r="F516" s="1">
+        <v>16.9</v>
+      </c>
+      <c r="G516" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H516" s="1">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="517" customHeight="1" spans="1:8">
+      <c r="A517" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E517" s="1">
+        <v>89.7</v>
+      </c>
+      <c r="F517" s="1">
+        <v>16.6</v>
+      </c>
+      <c r="G517" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H517" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="518" customHeight="1" spans="1:8">
+      <c r="A518" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E518" s="1">
+        <v>85.6</v>
+      </c>
+      <c r="F518" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="G518" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H518" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="519" customHeight="1" spans="1:8">
+      <c r="A519" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E519" s="1">
+        <v>110.3</v>
+      </c>
+      <c r="F519" s="1">
+        <v>14</v>
+      </c>
+      <c r="G519" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H519" s="1">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="520" customHeight="1" spans="1:8">
+      <c r="A520" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E520" s="1">
+        <v>111</v>
+      </c>
+      <c r="F520" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="G520" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H520" s="1">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="521" customHeight="1" spans="1:8">
+      <c r="A521" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C521" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D521" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E521" s="1">
+        <v>120.9</v>
+      </c>
+      <c r="F521" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="G521" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H521" s="1">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="522" customHeight="1" spans="1:8">
+      <c r="A522" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E522" s="1">
+        <v>82.1</v>
+      </c>
+      <c r="F522" s="1">
+        <v>12.3</v>
+      </c>
+      <c r="G522" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H522" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="523" customHeight="1" spans="1:8">
+      <c r="A523" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D523" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E523" s="1">
+        <v>116.2</v>
+      </c>
+      <c r="F523" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G523" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H523" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="524" customHeight="1" spans="1:8">
+      <c r="A524" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E524" s="1">
+        <v>135.1</v>
+      </c>
+      <c r="F524" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="G524" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H524" s="1">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="525" customHeight="1" spans="1:8">
+      <c r="A525" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E525" s="1">
+        <v>155.8</v>
+      </c>
+      <c r="F525" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G525" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H525" s="1">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="526" customHeight="1" spans="1:8">
+      <c r="A526" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E526" s="1">
+        <v>113.9</v>
+      </c>
+      <c r="F526" s="1">
+        <v>2</v>
+      </c>
+      <c r="G526" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H526" s="1">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="527" customHeight="1" spans="1:8">
+      <c r="A527" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E527" s="1">
+        <v>114.2</v>
+      </c>
+      <c r="F527" s="1">
+        <v>0</v>
+      </c>
+      <c r="G527" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H527" s="1">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="528" customHeight="1" spans="1:8">
+      <c r="A528" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E528" s="1">
+        <v>117.1</v>
+      </c>
+      <c r="F528" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="G528" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H528" s="1">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="529" customHeight="1" spans="1:8">
+      <c r="A529" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E529" s="1">
+        <v>118.7</v>
+      </c>
+      <c r="F529" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="G529" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H529" s="1">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="530" customHeight="1" spans="1:8">
+      <c r="A530" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C530" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D530" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E530" s="1">
+        <v>121.6</v>
+      </c>
+      <c r="F530" s="1">
+        <v>-4.1</v>
+      </c>
+      <c r="G530" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H530" s="1">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="531" customHeight="1" spans="1:8">
+      <c r="A531" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C531" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D531" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E531" s="1">
+        <v>132</v>
+      </c>
+      <c r="F531" s="1">
+        <v>-21.9</v>
+      </c>
+      <c r="G531" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H531" s="1">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="532" customHeight="1" spans="1:8">
+      <c r="A532" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C532" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D532" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E532" s="1">
+        <v>110.5</v>
+      </c>
+      <c r="F532" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="G532" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H532" s="1">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="533" customHeight="1" spans="1:8">
+      <c r="A533" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C533" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D533" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E533" s="1">
+        <v>80.3</v>
+      </c>
+      <c r="F533" s="1">
+        <v>20.4</v>
+      </c>
+      <c r="G533" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H533" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="534" customHeight="1" spans="1:8">
+      <c r="A534" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D534" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E534" s="1">
+        <v>137.1</v>
+      </c>
+      <c r="F534" s="1">
+        <v>16.9</v>
+      </c>
+      <c r="G534" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H534" s="1">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="535" customHeight="1" spans="1:8">
+      <c r="A535" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C535" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D535" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E535" s="1">
+        <v>86.6</v>
+      </c>
+      <c r="F535" s="1">
+        <v>16.6</v>
+      </c>
+      <c r="G535" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H535" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="536" customHeight="1" spans="1:8">
+      <c r="A536" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C536" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D536" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E536" s="1">
+        <v>89.6</v>
+      </c>
+      <c r="F536" s="1">
+        <v>16.4</v>
+      </c>
+      <c r="G536" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H536" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="537" customHeight="1" spans="1:8">
+      <c r="A537" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C537" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D537" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E537" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="F537" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="G537" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H537" s="1">
+        <v>9.8</v>
+      </c>
+    </row>
+    <row r="538" customHeight="1" spans="1:8">
+      <c r="A538" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C538" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D538" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E538" s="1">
+        <v>110.8</v>
+      </c>
+      <c r="F538" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="G538" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H538" s="1">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="539" customHeight="1" spans="1:8">
+      <c r="A539" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C539" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D539" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E539" s="1">
+        <v>121.5</v>
+      </c>
+      <c r="F539" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="G539" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H539" s="1">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="540" customHeight="1" spans="1:8">
+      <c r="A540" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D540" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E540" s="1">
+        <v>82</v>
+      </c>
+      <c r="F540" s="1">
+        <v>12.2</v>
+      </c>
+      <c r="G540" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H540" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="541" customHeight="1" spans="1:8">
+      <c r="A541" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C541" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D541" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E541" s="1">
+        <v>116.4</v>
+      </c>
+      <c r="F541" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="G541" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H541" s="1">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="542" customHeight="1" spans="1:8">
+      <c r="A542" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C542" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D542" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E542" s="1">
+        <v>134.9</v>
+      </c>
+      <c r="F542" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="G542" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H542" s="1">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="543" customHeight="1" spans="1:8">
+      <c r="A543" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C543" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D543" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E543" s="1">
+        <v>155.6</v>
+      </c>
+      <c r="F543" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="G543" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H543" s="1">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="544" customHeight="1" spans="1:8">
+      <c r="A544" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D544" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E544" s="1">
+        <v>113.4</v>
+      </c>
+      <c r="F544" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="G544" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H544" s="1">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="545" customHeight="1" spans="1:8">
+      <c r="A545" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D545" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E545" s="1">
+        <v>114</v>
+      </c>
+      <c r="F545" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="G545" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H545" s="1">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="546" customHeight="1" spans="1:8">
+      <c r="A546" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D546" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E546" s="1">
+        <v>117.1</v>
+      </c>
+      <c r="F546" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="G546" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H546" s="1">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="547" customHeight="1" spans="1:8">
+      <c r="A547" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C547" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E547" s="1">
+        <v>118.7</v>
+      </c>
+      <c r="F547" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="G547" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H547" s="1">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="548" customHeight="1" spans="1:8">
+      <c r="A548" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C548" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D548" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E548" s="1">
+        <v>120.9</v>
+      </c>
+      <c r="F548" s="1">
+        <v>-4.7</v>
+      </c>
+      <c r="G548" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H548" s="1">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="549" customHeight="1" spans="1:8">
+      <c r="A549" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C549" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D549" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E549" s="1">
+        <v>131.5</v>
+      </c>
+      <c r="F549" s="1">
+        <v>-22.2</v>
+      </c>
+      <c r="G549" s="1">
+        <v>100.2</v>
+      </c>
+      <c r="H549" s="1">
+        <v>31.3</v>
       </c>
     </row>
   </sheetData>
